--- a/organization.xlsx
+++ b/organization.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c308351cf5a860c7/github_oz/oz_youtube/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="506" documentId="13_ncr:1_{E080B429-C63D-4743-90CA-FFA68B47823D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A5E77F6-735E-4ADB-A974-355F876C1FE1}"/>
+  <xr:revisionPtr revIDLastSave="513" documentId="13_ncr:1_{E080B429-C63D-4743-90CA-FFA68B47823D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BC00130-28F9-4E3A-8BAB-71538B2E0397}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="556" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Periódicos" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Matriz!$A$1:$AC$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Matriz!$A$1:$AC$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Periódicos!$A$1:$N$168</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2969" uniqueCount="1116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2954" uniqueCount="1116">
   <si>
     <t>Indicador</t>
   </si>
@@ -3209,9 +3209,6 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=NfphOjG623Y</t>
-  </si>
-  <si>
-    <t>Warp Drive: The physics behind space warp</t>
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=-HVx9UttdIc</t>
@@ -3896,46 +3893,6 @@
 🧡 Patreon: https://www.patreon.com/ozsp12
 ✍️ Medium: https://medium.com/@ozsp12
 𝕏 X (Twitter): https://x.com/ozsp12
-📱 TikTok: https://www.tiktok.com/@ozsp12
-▶️ YouTube: https://www.youtube.com/@ozlsp12</t>
-  </si>
-  <si>
-    <t>Disclaimer: This is not a speculative or popular science presentation, but a pedagogical introduction grounded in the formalism of General Relativity.
-📌 Video Chapters (YouTube Chapters):
-00:00 - Introduction and Alcubierre's Proposal
-00:14 - The Warp Bubble and Spacetime Manipulation
-00:40 - The Wake Effect and Frame of Reference Transport
-00:50 - Physics Inside the Warp Bubble
-01:10 - 3+1 Formalism in General Relativity
-01:25 - The ADM Decomposition
-01:39 - Lapse and Deviation Vector: Fundamental Concepts
-02:06 - The Alcubierre Metric and the Bubble Impulse
-02:26 - Global Hyperbolicity and Preservation of Causality
-02:54 - Negative Energy and Violated Energy Conditions
-This video offers a concise and rigorous overview of the theoretical foundations of the Alcubierre Warp Drive, aimed at graduate students and researchers in General Relativity. The Alcubierre metric, introduced in 1994, describes a spacetime geometry that allows for effectively superluminal displacement by contracting space ahead of a warp bubble and expanding it behind it, without violating local causality or the speed-of-light limit within the bubble.
-Key concepts:
-Spacetime foliation in spatial hypersurfaces
-Definition and interpretation of the lapse function and deviation vector
-Structure of the Alcubierre metric
-Global hyperbolicity and preservation of causality
-Violation of classical energy conditions (Weak and Dominant)
-Role of exotic matter and implications for the energy-momentum tensor
-Reference:
-Alcubierre, M. (1994). The warp drive: hyper-fast travel within general relativity. Classical and Quantum Gravity, 11(5), L73. https://doi.org/10.1088/0264-9381/11/5/001
-arXiv: https://arxiv.org/abs/gr-qc/0009013
-Keywords:
-Alcubierre drive, warp bubble, general relativity, ADM formalism, spacetime geometry, Einstein's equations, exotic matter, causality, energy conditions
-#GeneralRelativity #TheoreticalPhysics #AlcubierreDrive #Spacetime #WarpDrive #Einstein #Interstellar #physics #foryou #foryoupage
-🔗 Follow me on social media:
-🌐 Webpage: https://ozsp12.github.io/
-✅ GitHub: https://github.com/ozsp12
-🧪 ResearchGate: https://www.researchgate.net/profile/Osvaldo-Santos-Pereira
-🔬 Google Scholar: https://scholar.google.com/citations?user=HIZp0X8AAAAJ&amp;hl=en
-🧾 ORCID: https://orcid.org/0000-0003-2231-517X
-💼 LinkedIn: https://www.linkedin.com/in/ozsp12
-🧡 Patreon: https://www.patreon.com/ozsp12
-✍️ Medium: https://medium.com/@ozsp12
-𝕏X (Twitter): https://x.com/ozsp12
 📱 TikTok: https://www.tiktok.com/@ozsp12
 ▶️ YouTube: https://www.youtube.com/@ozlsp12</t>
   </si>
@@ -4063,6 +4020,36 @@
   </si>
   <si>
     <t>Artigo publicado na RBEF</t>
+  </si>
+  <si>
+    <t>Warp Drive: A Física por Trás da Dobra Espacial</t>
+  </si>
+  <si>
+    <t>Aviso: Esta não é uma apresentação especulativa ou de divulgação científica, mas sim uma introdução pedagógica fundamentada no formalismo da Relatividade Geral.
+Capítulos do vídeo (YouTube Chapters):
+00:00 - Introdução e a proposta de Alcubierre
+00:14 - A bolha de dobra e a manipulação do espaço-tempo
+00:40 - O efeito de esteira e o transporte do referencial
+00:50 - Física no interior da bolha de dobra
+01:10 - Formalismo 3+1 na Relatividade Geral
+01:25 - A decomposição ADM
+01:39 - Função lapso e vetor de deslocamento: conceitos fundamentais
+02:06 - A métrica de Alcubierre e o impulso da bolha
+02:26 - Hiperbolicidade global e preservação da causalidade
+02:54 - Energia negativa e violação das condições de energia
+Este vídeo apresenta uma visão geral concisa e rigorosa dos fundamentos teóricos do Warp Drive de Alcubierre, destinada a estudantes de pós-graduação e pesquisadores em Relatividade Geral. A métrica de Alcubierre, introduzida em 1994, descreve uma geometria do espaço-tempo que permite um deslocamento efetivamente superluminal por meio da contração do espaço à frente de uma bolha de dobra e de sua expansão atrás dela, sem violar localmente a causalidade ou o limite da velocidade da luz no interior da bolha.
+Conceitos principais:
+Folheação do espaço-tempo em hipersuperfícies espaciais
+Definição e interpretação da função lapso e do vetor de deslocamento
+Estrutura da métrica de Alcubierre
+Hiperbolicidade global e preservação da causalidade
+Violação das condições clássicas de energia (Fraca e Dominante)
+Papel da matéria exótica e implicações para o tensor energia-momento
+Referência:
+Alcubierre, M. (1994). The warp drive: hyper-fast travel within general relativity. *Classical and Quantum Gravity*, 11(5), L73. [https://doi.org/10.1088/0264-9381/11/5/001](https://doi.org/10.1088/0264-9381/11/5/001)
+arXiv: [https://arxiv.org/abs/gr-qc/0009013](https://arxiv.org/abs/gr-qc/0009013)
+Palavras-chave:
+Warp drive de Alcubierre, bolha de dobra, relatividade geral, formalismo ADM, geometria do espaço-tempo, equações de Einstein, matéria exótica, causalidade, condições de energia</t>
   </si>
 </sst>
 </file>
@@ -4425,7 +4412,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4519,6 +4506,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -9732,7 +9720,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="34.049999999999997" customHeight="1">
       <c r="A1" s="37" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
@@ -9749,7 +9737,7 @@
     </row>
     <row r="2" spans="1:13" ht="14.25">
       <c r="A2" s="38" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
@@ -9781,15 +9769,15 @@
     </row>
     <row r="4" spans="1:13" ht="14.25">
       <c r="A4" s="34" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B4" s="32"/>
       <c r="C4" s="34" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="D4" s="32"/>
       <c r="E4" s="34" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="F4" s="32"/>
       <c r="G4" s="34" t="s">
@@ -9801,7 +9789,7 @@
       </c>
       <c r="J4" s="32"/>
       <c r="K4" s="34" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="L4" s="32"/>
       <c r="M4" s="4"/>
@@ -9856,44 +9844,44 @@
     </row>
     <row r="7" spans="1:13" ht="14.25">
       <c r="A7" s="34" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B7" s="32"/>
       <c r="C7" s="34" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="D7" s="32"/>
       <c r="E7" s="34" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="F7" s="32"/>
       <c r="G7" s="34" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="H7" s="32"/>
       <c r="I7" s="34" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="J7" s="32"/>
       <c r="K7" s="34" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="L7" s="32"/>
       <c r="M7" s="4"/>
     </row>
     <row r="8" spans="1:13" ht="28.05" customHeight="1">
       <c r="A8" s="35">
-        <f>COUNTIF(Matriz!$E$2:$E$48,"&gt;0")</f>
-        <v>47</v>
+        <f>COUNTIF(Matriz!$E$2:$E$47,"&gt;0")</f>
+        <v>46</v>
       </c>
       <c r="B8" s="36"/>
       <c r="C8" s="35">
-        <f>COUNTIF(Matriz!$E$2:$E$48,0)</f>
+        <f>COUNTIF(Matriz!$E$2:$E$47,0)</f>
         <v>0</v>
       </c>
       <c r="D8" s="36"/>
       <c r="E8" s="35">
-        <f>COUNTIF(Matriz!$E$2:$E$48,"&gt;=3")</f>
+        <f>COUNTIF(Matriz!$E$2:$E$47,"&gt;=3")</f>
         <v>8</v>
       </c>
       <c r="F8" s="36"/>
@@ -9946,7 +9934,7 @@
     </row>
     <row r="11" spans="1:13" ht="14.25">
       <c r="A11" s="31" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B11" s="32"/>
       <c r="C11" s="32"/>
@@ -9954,7 +9942,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="4"/>
       <c r="G11" s="31" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
@@ -9965,26 +9953,26 @@
     </row>
     <row r="12" spans="1:13" ht="14.25">
       <c r="A12" s="5" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>4</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="5" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>11</v>
@@ -9998,7 +9986,7 @@
     </row>
     <row r="13" spans="1:13" ht="14.25">
       <c r="A13" s="21" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B13" s="9" t="e">
         <f>COUNTIF(#REF!,$A13)/12</f>
@@ -10078,7 +10066,7 @@
     </row>
     <row r="15" spans="1:13" ht="14.25">
       <c r="A15" s="21" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B15" s="9" t="e">
         <f>COUNTIF(#REF!,$A15)/12</f>
@@ -10118,7 +10106,7 @@
     </row>
     <row r="16" spans="1:13" ht="14.25">
       <c r="A16" s="21" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B16" s="9" t="e">
         <f>COUNTIF(#REF!,$A16)/12</f>
@@ -10158,7 +10146,7 @@
     </row>
     <row r="17" spans="1:13" ht="14.25">
       <c r="A17" s="21" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B17" s="9" t="e">
         <f>COUNTIF(#REF!,$A17)/12</f>
@@ -10198,7 +10186,7 @@
     </row>
     <row r="18" spans="1:13" ht="14.25">
       <c r="A18" s="21" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B18" s="9" t="e">
         <f>COUNTIF(#REF!,$A18)/12</f>
@@ -10238,7 +10226,7 @@
     </row>
     <row r="19" spans="1:13" ht="14.25">
       <c r="A19" s="21" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B19" s="9" t="e">
         <f>COUNTIF(#REF!,$A19)/12</f>
@@ -10318,7 +10306,7 @@
     </row>
     <row r="21" spans="1:13" ht="14.25">
       <c r="A21" s="21" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B21" s="9" t="e">
         <f>COUNTIF(#REF!,$A21)/12</f>
@@ -10358,7 +10346,7 @@
     </row>
     <row r="22" spans="1:13" ht="14.25">
       <c r="A22" s="21" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B22" s="9" t="e">
         <f>COUNTIF(#REF!,$A22)/12</f>
@@ -10398,7 +10386,7 @@
     </row>
     <row r="23" spans="1:13" ht="14.25">
       <c r="A23" s="21" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B23" s="9" t="e">
         <f>COUNTIF(#REF!,$A23)/12</f>
@@ -10438,7 +10426,7 @@
     </row>
     <row r="24" spans="1:13" ht="14.25">
       <c r="A24" s="24" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B24" s="9" t="e">
         <f>COUNTIF(#REF!,$A24)/12</f>
@@ -10493,7 +10481,7 @@
     </row>
     <row r="26" spans="1:13" ht="14.25">
       <c r="A26" s="31" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
@@ -10501,7 +10489,7 @@
       <c r="E26" s="32"/>
       <c r="F26" s="4"/>
       <c r="G26" s="31" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
@@ -10512,10 +10500,10 @@
     </row>
     <row r="27" spans="1:13" ht="14.25">
       <c r="A27" s="14" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>11</v>
@@ -10524,10 +10512,10 @@
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="14" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
@@ -10852,7 +10840,7 @@
     </row>
     <row r="41" spans="1:13" ht="14.25">
       <c r="A41" s="31" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B41" s="32"/>
       <c r="C41" s="32"/>
@@ -10860,7 +10848,7 @@
       <c r="E41" s="32"/>
       <c r="F41" s="4"/>
       <c r="G41" s="31" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H41" s="32"/>
       <c r="I41" s="32"/>
@@ -10874,7 +10862,7 @@
         <v>25</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>3</v>
@@ -10904,11 +10892,11 @@
         <v/>
       </c>
       <c r="B43" s="9" t="str">
-        <f>IFERROR(INDEX(Matriz!$B$2:$B$48,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
+        <f>IFERROR(INDEX(Matriz!$B$2:$B$47,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
         <v/>
       </c>
       <c r="C43" s="9" t="str">
-        <f>IFERROR(INDEX(Matriz!$E$2:$E$48,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
+        <f>IFERROR(INDEX(Matriz!$E$2:$E$47,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
         <v/>
       </c>
       <c r="D43" s="9" t="str">
@@ -10921,7 +10909,7 @@
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="8" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="H43" s="22">
         <f>COUNTA(Periódicos!$A$2:$A$168)</f>
@@ -10939,11 +10927,11 @@
         <v/>
       </c>
       <c r="B44" s="9" t="str">
-        <f>IFERROR(INDEX(Matriz!$B$2:$B$48,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
+        <f>IFERROR(INDEX(Matriz!$B$2:$B$47,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
         <v/>
       </c>
       <c r="C44" s="9" t="str">
-        <f>IFERROR(INDEX(Matriz!$E$2:$E$48,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
+        <f>IFERROR(INDEX(Matriz!$E$2:$E$47,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
         <v/>
       </c>
       <c r="D44" s="9" t="str">
@@ -10956,7 +10944,7 @@
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="8" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H44" s="22">
         <f>COUNTIF(Periódicos!$I$2:$I$168,5)</f>
@@ -10974,11 +10962,11 @@
         <v/>
       </c>
       <c r="B45" s="9" t="str">
-        <f>IFERROR(INDEX(Matriz!$B$2:$B$48,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
+        <f>IFERROR(INDEX(Matriz!$B$2:$B$47,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
         <v/>
       </c>
       <c r="C45" s="9" t="str">
-        <f>IFERROR(INDEX(Matriz!$E$2:$E$48,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
+        <f>IFERROR(INDEX(Matriz!$E$2:$E$47,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
         <v/>
       </c>
       <c r="D45" s="9" t="str">
@@ -10991,7 +10979,7 @@
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="8" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H45" s="22">
         <f>COUNTIF(Periódicos!$I$2:$I$168,"&gt;=4")</f>
@@ -11009,11 +10997,11 @@
         <v/>
       </c>
       <c r="B46" s="9" t="str">
-        <f>IFERROR(INDEX(Matriz!$B$2:$B$48,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
+        <f>IFERROR(INDEX(Matriz!$B$2:$B$47,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
         <v/>
       </c>
       <c r="C46" s="9" t="str">
-        <f>IFERROR(INDEX(Matriz!$E$2:$E$48,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
+        <f>IFERROR(INDEX(Matriz!$E$2:$E$47,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
         <v/>
       </c>
       <c r="D46" s="9" t="str">
@@ -11026,7 +11014,7 @@
       </c>
       <c r="F46" s="4"/>
       <c r="G46" s="8" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H46" s="23">
         <f>IFERROR(AVERAGE(Periódicos!$D$2:$D$168),0)</f>
@@ -11044,11 +11032,11 @@
         <v/>
       </c>
       <c r="B47" s="9" t="str">
-        <f>IFERROR(INDEX(Matriz!$B$2:$B$48,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
+        <f>IFERROR(INDEX(Matriz!$B$2:$B$47,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
         <v/>
       </c>
       <c r="C47" s="9" t="str">
-        <f>IFERROR(INDEX(Matriz!$E$2:$E$48,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
+        <f>IFERROR(INDEX(Matriz!$E$2:$E$47,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
         <v/>
       </c>
       <c r="D47" s="9" t="str">
@@ -11079,11 +11067,11 @@
         <v/>
       </c>
       <c r="B48" s="9" t="str">
-        <f>IFERROR(INDEX(Matriz!$B$2:$B$48,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
+        <f>IFERROR(INDEX(Matriz!$B$2:$B$47,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
         <v/>
       </c>
       <c r="C48" s="9" t="str">
-        <f>IFERROR(INDEX(Matriz!$E$2:$E$48,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
+        <f>IFERROR(INDEX(Matriz!$E$2:$E$47,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
         <v/>
       </c>
       <c r="D48" s="9" t="str">
@@ -11114,11 +11102,11 @@
         <v/>
       </c>
       <c r="B49" s="9" t="str">
-        <f>IFERROR(INDEX(Matriz!$B$2:$B$48,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
+        <f>IFERROR(INDEX(Matriz!$B$2:$B$47,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
         <v/>
       </c>
       <c r="C49" s="9" t="str">
-        <f>IFERROR(INDEX(Matriz!$E$2:$E$48,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
+        <f>IFERROR(INDEX(Matriz!$E$2:$E$47,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
         <v/>
       </c>
       <c r="D49" s="9" t="str">
@@ -11149,11 +11137,11 @@
         <v/>
       </c>
       <c r="B50" s="9" t="str">
-        <f>IFERROR(INDEX(Matriz!$B$2:$B$48,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
+        <f>IFERROR(INDEX(Matriz!$B$2:$B$47,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
         <v/>
       </c>
       <c r="C50" s="9" t="str">
-        <f>IFERROR(INDEX(Matriz!$E$2:$E$48,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
+        <f>IFERROR(INDEX(Matriz!$E$2:$E$47,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
         <v/>
       </c>
       <c r="D50" s="9" t="str">
@@ -11166,7 +11154,7 @@
       </c>
       <c r="F50" s="4"/>
       <c r="G50" s="8" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="H50" s="22">
         <f>COUNTIF(Periódicos!$K$2:$K$168,"Open Access*")</f>
@@ -11184,11 +11172,11 @@
         <v/>
       </c>
       <c r="B51" s="9" t="str">
-        <f>IFERROR(INDEX(Matriz!$B$2:$B$48,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
+        <f>IFERROR(INDEX(Matriz!$B$2:$B$47,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
         <v/>
       </c>
       <c r="C51" s="9" t="str">
-        <f>IFERROR(INDEX(Matriz!$E$2:$E$48,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
+        <f>IFERROR(INDEX(Matriz!$E$2:$E$47,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
         <v/>
       </c>
       <c r="D51" s="9" t="str">
@@ -11201,7 +11189,7 @@
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="8" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H51" s="22" t="e">
         <f>COUNTIF(#REF!,"Journal")</f>
@@ -11219,11 +11207,11 @@
         <v/>
       </c>
       <c r="B52" s="9" t="str">
-        <f>IFERROR(INDEX(Matriz!$B$2:$B$48,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
+        <f>IFERROR(INDEX(Matriz!$B$2:$B$47,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
         <v/>
       </c>
       <c r="C52" s="9" t="str">
-        <f>IFERROR(INDEX(Matriz!$E$2:$E$48,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
+        <f>IFERROR(INDEX(Matriz!$E$2:$E$47,MATCH(ROW()-42,Matriz!#REF!,0)),"")</f>
         <v/>
       </c>
       <c r="D52" s="9" t="str">
@@ -11236,7 +11224,7 @@
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="11" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H52" s="25" t="e">
         <f>$H$14</f>
@@ -11265,7 +11253,7 @@
     </row>
     <row r="54" spans="1:13" ht="14.25">
       <c r="A54" s="33" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B54" s="32"/>
       <c r="C54" s="32"/>
@@ -11282,17 +11270,17 @@
     </row>
     <row r="55" spans="1:13" ht="14.25">
       <c r="A55" s="26" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B55" s="27" t="s">
         <v>1044</v>
-      </c>
-      <c r="B55" s="27" t="s">
-        <v>1045</v>
       </c>
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
       <c r="G55" s="28" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
@@ -11303,7 +11291,7 @@
     </row>
     <row r="56" spans="1:13" ht="14.25">
       <c r="A56" s="8" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B56" s="17" t="e">
         <f>COUNTIFS(#REF!,1,#REF!,"")</f>
@@ -11314,7 +11302,7 @@
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
       <c r="G56" s="4" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="H56" s="4" t="e">
         <f>$E$5</f>
@@ -11328,7 +11316,7 @@
     </row>
     <row r="57" spans="1:13" ht="14.25">
       <c r="A57" s="8" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B57" s="17" t="e">
         <f>COUNTIFS(#REF!,"&lt;&gt;",#REF!,0)</f>
@@ -11339,7 +11327,7 @@
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
       <c r="G57" s="4" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="H57" s="29" t="e">
         <f>$C$5-$E$5</f>
@@ -11353,7 +11341,7 @@
     </row>
     <row r="58" spans="1:13" ht="14.25">
       <c r="A58" s="8" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B58" s="17" t="e">
         <f>COUNTIFS(#REF!,1,#REF!,"")</f>
@@ -11373,10 +11361,10 @@
     </row>
     <row r="59" spans="1:13" ht="14.25">
       <c r="A59" s="8" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B59" s="17">
-        <f>COUNTBLANK(Matriz!$B$2:$B$48)</f>
+        <f>COUNTBLANK(Matriz!$B$2:$B$47)</f>
         <v>0</v>
       </c>
       <c r="C59" s="4"/>
@@ -11393,7 +11381,7 @@
     </row>
     <row r="60" spans="1:13" ht="14.25">
       <c r="A60" s="11" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B60" s="19">
         <f>COUNTBLANK(Periódicos!$D$2:$D$168)</f>
@@ -11454,7 +11442,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B93DC578-2EEA-48CF-9EFD-E294C2F4F9E2}">
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="4" style="30" customWidth="1"/>
@@ -11472,10 +11460,10 @@
         <v>24</v>
       </c>
       <c r="B1" s="43" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C1" s="43" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="D1" s="43" t="s">
         <v>26</v>
@@ -11520,40 +11508,40 @@
         <v>23</v>
       </c>
       <c r="R1" s="43" t="s">
+        <v>1053</v>
+      </c>
+      <c r="S1" s="43" t="s">
         <v>1054</v>
       </c>
-      <c r="S1" s="43" t="s">
+      <c r="T1" s="43" t="s">
         <v>1055</v>
       </c>
-      <c r="T1" s="43" t="s">
+      <c r="U1" s="43" t="s">
         <v>1056</v>
       </c>
-      <c r="U1" s="43" t="s">
+      <c r="V1" s="43" t="s">
         <v>1057</v>
       </c>
-      <c r="V1" s="43" t="s">
+      <c r="W1" s="43" t="s">
         <v>1058</v>
       </c>
-      <c r="W1" s="43" t="s">
+      <c r="X1" s="43" t="s">
         <v>1059</v>
       </c>
-      <c r="X1" s="43" t="s">
+      <c r="Y1" s="43" t="s">
         <v>1060</v>
       </c>
-      <c r="Y1" s="43" t="s">
+      <c r="Z1" s="43" t="s">
         <v>1061</v>
       </c>
-      <c r="Z1" s="43" t="s">
+      <c r="AA1" s="43" t="s">
         <v>1062</v>
       </c>
-      <c r="AA1" s="43" t="s">
+      <c r="AB1" s="43" t="s">
         <v>1063</v>
       </c>
-      <c r="AB1" s="43" t="s">
+      <c r="AC1" s="44" t="s">
         <v>1064</v>
-      </c>
-      <c r="AC1" s="44" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="14.35" customHeight="1">
@@ -11561,13 +11549,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="45" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D2" s="45" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="E2" s="48">
         <v>1</v>
@@ -11608,41 +11596,41 @@
       <c r="Q2" s="47">
         <v>0</v>
       </c>
-      <c r="R2" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S2" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T2" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U2" s="49" t="s">
-        <v>1003</v>
-      </c>
-      <c r="V2" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W2" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X2" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y2" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z2" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA2" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB2" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC2" s="49" t="s">
-        <v>1110</v>
+      <c r="R2" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S2" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T2" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U2" s="50" t="s">
+        <v>1002</v>
+      </c>
+      <c r="V2" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W2" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X2" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y2" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z2" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA2" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB2" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC2" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="14.35" customHeight="1">
@@ -11650,13 +11638,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="45" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="C3" s="46" t="s">
         <v>971</v>
       </c>
       <c r="D3" s="46" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="E3" s="48">
         <v>1</v>
@@ -11697,41 +11685,41 @@
       <c r="Q3" s="47">
         <v>0</v>
       </c>
-      <c r="R3" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S3" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T3" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U3" s="49" t="s">
+      <c r="R3" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S3" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T3" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U3" s="50" t="s">
         <v>972</v>
       </c>
-      <c r="V3" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W3" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X3" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y3" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z3" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA3" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB3" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC3" s="49" t="s">
-        <v>1110</v>
+      <c r="V3" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W3" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X3" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y3" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z3" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA3" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB3" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC3" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="14.35" customHeight="1">
@@ -11739,13 +11727,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="45" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="C4" s="46" t="s">
         <v>980</v>
       </c>
       <c r="D4" s="46" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E4" s="48">
         <v>1</v>
@@ -11786,41 +11774,41 @@
       <c r="Q4" s="47">
         <v>0</v>
       </c>
-      <c r="R4" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S4" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T4" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U4" s="49" t="s">
+      <c r="R4" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S4" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T4" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U4" s="50" t="s">
         <v>981</v>
       </c>
-      <c r="V4" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W4" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X4" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y4" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z4" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA4" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB4" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC4" s="49" t="s">
-        <v>1110</v>
+      <c r="V4" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W4" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X4" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y4" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z4" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA4" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB4" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC4" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="14.35" customHeight="1">
@@ -11828,13 +11816,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="45" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="C5" s="46" t="s">
         <v>955</v>
       </c>
       <c r="D5" s="46" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E5" s="48">
         <v>1</v>
@@ -11875,41 +11863,41 @@
       <c r="Q5" s="47">
         <v>0</v>
       </c>
-      <c r="R5" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S5" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T5" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U5" s="49" t="s">
+      <c r="R5" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S5" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T5" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U5" s="50" t="s">
         <v>956</v>
       </c>
-      <c r="V5" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W5" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X5" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y5" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z5" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA5" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB5" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC5" s="49" t="s">
-        <v>1110</v>
+      <c r="V5" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W5" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X5" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y5" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z5" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA5" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB5" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC5" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="14.35" customHeight="1">
@@ -11917,13 +11905,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="45" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="C6" s="46" t="s">
         <v>948</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="E6" s="48">
         <v>1</v>
@@ -11964,41 +11952,41 @@
       <c r="Q6" s="47">
         <v>0</v>
       </c>
-      <c r="R6" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S6" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T6" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U6" s="49" t="s">
+      <c r="R6" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S6" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T6" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U6" s="50" t="s">
         <v>949</v>
       </c>
-      <c r="V6" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W6" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X6" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y6" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z6" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA6" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB6" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC6" s="49" t="s">
-        <v>1110</v>
+      <c r="V6" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W6" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X6" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y6" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z6" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA6" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB6" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC6" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="14.35" customHeight="1">
@@ -12006,13 +11994,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="45" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="C7" s="46" t="s">
         <v>946</v>
       </c>
       <c r="D7" s="46" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="E7" s="48">
         <v>1</v>
@@ -12053,41 +12041,41 @@
       <c r="Q7" s="47">
         <v>0</v>
       </c>
-      <c r="R7" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S7" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T7" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U7" s="49" t="s">
+      <c r="R7" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S7" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T7" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U7" s="50" t="s">
         <v>947</v>
       </c>
-      <c r="V7" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W7" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X7" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y7" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z7" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA7" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB7" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC7" s="49" t="s">
-        <v>1110</v>
+      <c r="V7" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W7" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X7" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y7" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z7" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA7" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB7" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC7" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="14.35" customHeight="1">
@@ -12095,13 +12083,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="45" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="C8" s="46" t="s">
         <v>936</v>
       </c>
       <c r="D8" s="46" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="E8" s="48">
         <v>1</v>
@@ -12142,41 +12130,41 @@
       <c r="Q8" s="47">
         <v>0</v>
       </c>
-      <c r="R8" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S8" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T8" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U8" s="49" t="s">
+      <c r="R8" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S8" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T8" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U8" s="50" t="s">
         <v>937</v>
       </c>
-      <c r="V8" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W8" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X8" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y8" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z8" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA8" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB8" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC8" s="49" t="s">
-        <v>1110</v>
+      <c r="V8" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W8" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X8" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y8" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z8" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA8" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB8" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC8" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="14.35" customHeight="1">
@@ -12184,13 +12172,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="45" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="C9" s="46" t="s">
         <v>938</v>
       </c>
       <c r="D9" s="46" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="E9" s="48">
         <v>1</v>
@@ -12231,41 +12219,41 @@
       <c r="Q9" s="47">
         <v>0</v>
       </c>
-      <c r="R9" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S9" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T9" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U9" s="49" t="s">
+      <c r="R9" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S9" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T9" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U9" s="50" t="s">
         <v>939</v>
       </c>
-      <c r="V9" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W9" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X9" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y9" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z9" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA9" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB9" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC9" s="49" t="s">
-        <v>1110</v>
+      <c r="V9" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W9" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X9" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y9" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z9" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA9" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB9" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC9" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="14.35" customHeight="1">
@@ -12273,13 +12261,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="45" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="C10" s="46" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D10" s="46" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="E10" s="48">
         <v>1</v>
@@ -12320,41 +12308,41 @@
       <c r="Q10" s="47">
         <v>0</v>
       </c>
-      <c r="R10" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S10" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T10" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U10" s="49" t="s">
-        <v>1001</v>
-      </c>
-      <c r="V10" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W10" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X10" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y10" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z10" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA10" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB10" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC10" s="49" t="s">
-        <v>1110</v>
+      <c r="R10" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S10" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T10" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U10" s="50" t="s">
+        <v>1000</v>
+      </c>
+      <c r="V10" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W10" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X10" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y10" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z10" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA10" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB10" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC10" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="14.35" customHeight="1">
@@ -12362,13 +12350,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="45" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="C11" s="46" t="s">
         <v>959</v>
       </c>
       <c r="D11" s="46" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="E11" s="48">
         <v>1</v>
@@ -12409,41 +12397,41 @@
       <c r="Q11" s="47">
         <v>0</v>
       </c>
-      <c r="R11" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S11" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T11" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U11" s="49" t="s">
+      <c r="R11" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S11" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T11" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U11" s="50" t="s">
         <v>960</v>
       </c>
-      <c r="V11" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W11" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X11" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y11" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z11" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA11" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB11" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC11" s="49" t="s">
-        <v>1110</v>
+      <c r="V11" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W11" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X11" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y11" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z11" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA11" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB11" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC11" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="14.35" customHeight="1">
@@ -12451,13 +12439,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="C12" s="46" t="s">
         <v>965</v>
       </c>
       <c r="D12" s="45" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="E12" s="48">
         <v>1</v>
@@ -12498,41 +12486,41 @@
       <c r="Q12" s="47">
         <v>0</v>
       </c>
-      <c r="R12" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S12" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T12" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U12" s="49" t="s">
+      <c r="R12" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S12" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T12" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U12" s="50" t="s">
         <v>966</v>
       </c>
-      <c r="V12" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W12" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X12" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y12" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z12" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA12" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB12" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC12" s="49" t="s">
-        <v>1110</v>
+      <c r="V12" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W12" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X12" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y12" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z12" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA12" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB12" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC12" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="14.35" customHeight="1">
@@ -12540,13 +12528,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="45" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="C13" s="46" t="s">
         <v>961</v>
       </c>
       <c r="D13" s="46" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="E13" s="48">
         <v>1</v>
@@ -12587,41 +12575,41 @@
       <c r="Q13" s="47">
         <v>0</v>
       </c>
-      <c r="R13" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S13" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T13" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U13" s="49" t="s">
+      <c r="R13" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S13" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T13" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U13" s="50" t="s">
         <v>962</v>
       </c>
-      <c r="V13" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W13" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X13" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y13" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z13" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA13" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB13" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC13" s="49" t="s">
-        <v>1110</v>
+      <c r="V13" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W13" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X13" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y13" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z13" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA13" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB13" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC13" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="14.35" customHeight="1">
@@ -12629,13 +12617,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="45" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="C14" s="46" t="s">
         <v>973</v>
       </c>
       <c r="D14" s="46" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="E14" s="48">
         <v>1</v>
@@ -12676,41 +12664,41 @@
       <c r="Q14" s="47">
         <v>0</v>
       </c>
-      <c r="R14" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S14" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T14" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U14" s="49" t="s">
+      <c r="R14" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S14" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T14" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U14" s="50" t="s">
         <v>974</v>
       </c>
-      <c r="V14" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W14" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X14" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y14" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z14" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA14" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB14" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC14" s="49" t="s">
-        <v>1110</v>
+      <c r="V14" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W14" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X14" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y14" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z14" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA14" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB14" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC14" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="14.35" customHeight="1">
@@ -12718,13 +12706,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="45" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C15" s="46" t="s">
         <v>932</v>
       </c>
       <c r="D15" s="46" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="E15" s="48">
         <v>1</v>
@@ -12765,41 +12753,41 @@
       <c r="Q15" s="47">
         <v>0</v>
       </c>
-      <c r="R15" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S15" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T15" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U15" s="49" t="s">
+      <c r="R15" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S15" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T15" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U15" s="50" t="s">
         <v>933</v>
       </c>
-      <c r="V15" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W15" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X15" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y15" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z15" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA15" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB15" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC15" s="49" t="s">
-        <v>1110</v>
+      <c r="V15" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W15" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X15" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y15" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z15" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA15" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB15" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC15" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="16" spans="1:29" ht="14.35" customHeight="1">
@@ -12807,13 +12795,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="45" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C16" s="45" t="s">
         <v>975</v>
       </c>
       <c r="D16" s="46" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="E16" s="48">
         <v>1</v>
@@ -12854,41 +12842,41 @@
       <c r="Q16" s="47">
         <v>0</v>
       </c>
-      <c r="R16" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S16" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T16" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U16" s="49" t="s">
+      <c r="R16" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S16" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T16" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U16" s="50" t="s">
         <v>976</v>
       </c>
-      <c r="V16" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W16" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X16" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y16" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z16" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA16" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB16" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC16" s="49" t="s">
-        <v>1110</v>
+      <c r="V16" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W16" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X16" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y16" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z16" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA16" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB16" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC16" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="17" spans="1:29" ht="14.35" customHeight="1">
@@ -12896,13 +12884,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="45" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C17" s="45" t="s">
         <v>950</v>
       </c>
       <c r="D17" s="41" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="E17" s="48">
         <v>5</v>
@@ -12943,41 +12931,41 @@
       <c r="Q17" s="47">
         <v>0</v>
       </c>
-      <c r="R17" s="49" t="s">
+      <c r="R17" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="S17" s="49" t="s">
+      <c r="S17" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="T17" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U17" s="49" t="s">
+      <c r="T17" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U17" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="V17" s="49" t="s">
+      <c r="V17" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="W17" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X17" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y17" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z17" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA17" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB17" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC17" s="49" t="s">
-        <v>1110</v>
+      <c r="W17" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X17" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y17" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z17" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA17" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB17" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC17" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="18" spans="1:29" ht="14.35" customHeight="1">
@@ -12985,13 +12973,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="45" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C18" s="45" t="s">
         <v>31</v>
       </c>
       <c r="D18" s="45" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="E18" s="48">
         <v>4</v>
@@ -13032,41 +13020,41 @@
       <c r="Q18" s="47">
         <v>0</v>
       </c>
-      <c r="R18" s="49" t="s">
+      <c r="R18" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="S18" s="49" t="s">
+      <c r="S18" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="T18" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U18" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="V18" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W18" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X18" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y18" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z18" s="49" t="s">
-        <v>1114</v>
-      </c>
-      <c r="AA18" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB18" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC18" s="49" t="s">
-        <v>1110</v>
+      <c r="T18" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U18" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="V18" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W18" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X18" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y18" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z18" s="50" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AA18" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB18" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC18" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="19" spans="1:29" ht="14.35" customHeight="1">
@@ -13074,13 +13062,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="45" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C19" s="46" t="s">
         <v>928</v>
       </c>
       <c r="D19" s="46" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="E19" s="48">
         <v>1</v>
@@ -13121,41 +13109,41 @@
       <c r="Q19" s="47">
         <v>0</v>
       </c>
-      <c r="R19" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S19" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T19" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U19" s="49" t="s">
+      <c r="R19" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S19" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T19" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U19" s="50" t="s">
         <v>929</v>
       </c>
-      <c r="V19" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W19" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X19" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y19" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z19" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA19" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB19" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC19" s="49" t="s">
-        <v>1110</v>
+      <c r="V19" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W19" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X19" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y19" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z19" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA19" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB19" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC19" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="20" spans="1:29" ht="14.35" customHeight="1">
@@ -13163,13 +13151,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="45" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C20" s="46" t="s">
         <v>992</v>
       </c>
       <c r="D20" s="46" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="E20" s="48">
         <v>1</v>
@@ -13210,41 +13198,41 @@
       <c r="Q20" s="47">
         <v>0</v>
       </c>
-      <c r="R20" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S20" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T20" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U20" s="49" t="s">
+      <c r="R20" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S20" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T20" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U20" s="50" t="s">
         <v>993</v>
       </c>
-      <c r="V20" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W20" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X20" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y20" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z20" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA20" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB20" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC20" s="49" t="s">
-        <v>1110</v>
+      <c r="V20" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W20" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X20" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y20" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z20" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA20" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB20" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC20" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="21" spans="1:29" ht="14.35" customHeight="1">
@@ -13252,13 +13240,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="45" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C21" s="46" t="s">
         <v>934</v>
       </c>
       <c r="D21" s="46" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="E21" s="48">
         <v>1</v>
@@ -13299,41 +13287,41 @@
       <c r="Q21" s="47">
         <v>0</v>
       </c>
-      <c r="R21" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S21" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T21" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U21" s="49" t="s">
+      <c r="R21" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S21" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T21" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U21" s="50" t="s">
         <v>935</v>
       </c>
-      <c r="V21" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W21" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X21" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y21" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z21" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA21" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB21" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC21" s="49" t="s">
-        <v>1110</v>
+      <c r="V21" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W21" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X21" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y21" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z21" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA21" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB21" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC21" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="22" spans="1:29" ht="14.35" customHeight="1">
@@ -13341,13 +13329,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="45" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C22" s="46" t="s">
         <v>986</v>
       </c>
       <c r="D22" s="46" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="E22" s="48">
         <v>1</v>
@@ -13388,41 +13376,41 @@
       <c r="Q22" s="47">
         <v>0</v>
       </c>
-      <c r="R22" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S22" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T22" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U22" s="49" t="s">
+      <c r="R22" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S22" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T22" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U22" s="50" t="s">
         <v>987</v>
       </c>
-      <c r="V22" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W22" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X22" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y22" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z22" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA22" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB22" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC22" s="49" t="s">
-        <v>1110</v>
+      <c r="V22" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W22" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X22" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y22" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z22" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA22" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB22" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC22" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="23" spans="1:29" ht="14.35" customHeight="1">
@@ -13430,13 +13418,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C23" s="46" t="s">
         <v>990</v>
       </c>
       <c r="D23" s="46" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="E23" s="48">
         <v>1</v>
@@ -13477,41 +13465,41 @@
       <c r="Q23" s="47">
         <v>0</v>
       </c>
-      <c r="R23" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S23" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T23" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U23" s="49" t="s">
+      <c r="R23" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S23" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T23" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U23" s="50" t="s">
         <v>991</v>
       </c>
-      <c r="V23" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W23" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X23" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y23" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z23" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA23" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB23" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC23" s="49" t="s">
-        <v>1110</v>
+      <c r="V23" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W23" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X23" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y23" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z23" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA23" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB23" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC23" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="24" spans="1:29" ht="14.35" customHeight="1">
@@ -13519,13 +13507,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="45" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C24" s="46" t="s">
         <v>944</v>
       </c>
       <c r="D24" s="46" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="E24" s="48">
         <v>1</v>
@@ -13566,41 +13554,41 @@
       <c r="Q24" s="47">
         <v>0</v>
       </c>
-      <c r="R24" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S24" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T24" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U24" s="49" t="s">
+      <c r="R24" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S24" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T24" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U24" s="50" t="s">
         <v>945</v>
       </c>
-      <c r="V24" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W24" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X24" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y24" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z24" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA24" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB24" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC24" s="49" t="s">
-        <v>1110</v>
+      <c r="V24" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W24" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X24" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y24" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z24" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA24" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB24" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC24" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="25" spans="1:29" ht="14.35" customHeight="1">
@@ -13608,13 +13596,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="45" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C25" s="46" t="s">
         <v>969</v>
       </c>
       <c r="D25" s="46" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E25" s="48">
         <v>1</v>
@@ -13655,41 +13643,41 @@
       <c r="Q25" s="47">
         <v>0</v>
       </c>
-      <c r="R25" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S25" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T25" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U25" s="49" t="s">
+      <c r="R25" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S25" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T25" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U25" s="50" t="s">
         <v>970</v>
       </c>
-      <c r="V25" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W25" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X25" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y25" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z25" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA25" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB25" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC25" s="49" t="s">
-        <v>1110</v>
+      <c r="V25" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W25" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X25" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y25" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z25" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA25" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB25" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC25" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="26" spans="1:29" ht="14.35" customHeight="1">
@@ -13697,13 +13685,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="45" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C26" s="46" t="s">
         <v>953</v>
       </c>
       <c r="D26" s="46" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="E26" s="48">
         <v>1</v>
@@ -13744,41 +13732,41 @@
       <c r="Q26" s="47">
         <v>0</v>
       </c>
-      <c r="R26" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S26" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T26" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U26" s="49" t="s">
+      <c r="R26" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S26" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T26" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U26" s="50" t="s">
         <v>954</v>
       </c>
-      <c r="V26" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W26" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X26" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y26" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z26" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA26" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB26" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC26" s="49" t="s">
-        <v>1110</v>
+      <c r="V26" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W26" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X26" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y26" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z26" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA26" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB26" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC26" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="27" spans="1:29" ht="14.35" customHeight="1">
@@ -13786,13 +13774,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="45" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="C27" s="46" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D27" s="46" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="E27" s="48">
         <v>1</v>
@@ -13833,41 +13821,41 @@
       <c r="Q27" s="47">
         <v>0</v>
       </c>
-      <c r="R27" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S27" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T27" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U27" s="49" t="s">
-        <v>999</v>
-      </c>
-      <c r="V27" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W27" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X27" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y27" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z27" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA27" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB27" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC27" s="49" t="s">
-        <v>1110</v>
+      <c r="R27" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S27" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T27" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U27" s="50" t="s">
+        <v>998</v>
+      </c>
+      <c r="V27" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W27" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X27" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y27" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z27" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA27" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB27" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC27" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="28" spans="1:29" ht="14.35" customHeight="1">
@@ -13875,13 +13863,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="45" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C28" s="46" t="s">
         <v>982</v>
       </c>
       <c r="D28" s="46" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="E28" s="48">
         <v>1</v>
@@ -13922,41 +13910,41 @@
       <c r="Q28" s="47">
         <v>0</v>
       </c>
-      <c r="R28" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S28" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T28" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U28" s="49" t="s">
+      <c r="R28" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S28" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T28" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U28" s="50" t="s">
         <v>983</v>
       </c>
-      <c r="V28" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W28" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X28" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y28" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z28" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA28" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB28" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC28" s="49" t="s">
-        <v>1110</v>
+      <c r="V28" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W28" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X28" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y28" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z28" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA28" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB28" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC28" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="29" spans="1:29" ht="14.35" customHeight="1">
@@ -13964,13 +13952,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="45" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C29" s="46" t="s">
         <v>984</v>
       </c>
       <c r="D29" s="46" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="E29" s="48">
         <v>1</v>
@@ -14011,41 +13999,41 @@
       <c r="Q29" s="47">
         <v>0</v>
       </c>
-      <c r="R29" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S29" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T29" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U29" s="49" t="s">
+      <c r="R29" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S29" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T29" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U29" s="50" t="s">
         <v>985</v>
       </c>
-      <c r="V29" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W29" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X29" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y29" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z29" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA29" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB29" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC29" s="49" t="s">
-        <v>1110</v>
+      <c r="V29" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W29" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X29" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y29" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z29" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA29" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB29" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC29" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="30" spans="1:29" ht="14.35" customHeight="1">
@@ -14053,13 +14041,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="45" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C30" s="46" t="s">
         <v>940</v>
       </c>
       <c r="D30" s="46" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="E30" s="48">
         <v>1</v>
@@ -14100,41 +14088,41 @@
       <c r="Q30" s="47">
         <v>0</v>
       </c>
-      <c r="R30" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S30" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T30" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U30" s="49" t="s">
+      <c r="R30" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S30" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T30" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U30" s="50" t="s">
         <v>941</v>
       </c>
-      <c r="V30" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W30" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X30" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y30" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z30" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA30" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB30" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC30" s="49" t="s">
-        <v>1110</v>
+      <c r="V30" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W30" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X30" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y30" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z30" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA30" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB30" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC30" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="31" spans="1:29" ht="14.35" customHeight="1">
@@ -14142,13 +14130,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="45" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C31" s="46" t="s">
         <v>988</v>
       </c>
       <c r="D31" s="46" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E31" s="48">
         <v>1</v>
@@ -14189,41 +14177,41 @@
       <c r="Q31" s="47">
         <v>0</v>
       </c>
-      <c r="R31" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S31" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T31" s="49" t="s">
-        <v>1110</v>
+      <c r="R31" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S31" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T31" s="50" t="s">
+        <v>1108</v>
       </c>
       <c r="U31" s="49" t="s">
         <v>989</v>
       </c>
-      <c r="V31" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W31" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X31" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y31" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z31" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA31" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB31" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC31" s="49" t="s">
-        <v>1110</v>
+      <c r="V31" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W31" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X31" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y31" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z31" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA31" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB31" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC31" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="32" spans="1:29" ht="14.35" customHeight="1">
@@ -14231,13 +14219,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="45" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C32" s="46" t="s">
         <v>942</v>
       </c>
       <c r="D32" s="46" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="E32" s="48">
         <v>1</v>
@@ -14278,41 +14266,41 @@
       <c r="Q32" s="47">
         <v>0</v>
       </c>
-      <c r="R32" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S32" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T32" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U32" s="49" t="s">
+      <c r="R32" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S32" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T32" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U32" s="50" t="s">
         <v>943</v>
       </c>
-      <c r="V32" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W32" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X32" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y32" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z32" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA32" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB32" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC32" s="49" t="s">
-        <v>1110</v>
+      <c r="V32" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W32" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X32" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y32" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z32" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA32" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB32" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC32" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="33" spans="1:29" ht="14.35" customHeight="1">
@@ -14320,13 +14308,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="45" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C33" s="46" t="s">
         <v>977</v>
       </c>
       <c r="D33" s="46" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="E33" s="48">
         <v>1</v>
@@ -14367,41 +14355,41 @@
       <c r="Q33" s="47">
         <v>0</v>
       </c>
-      <c r="R33" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S33" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T33" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U33" s="49" t="s">
+      <c r="R33" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S33" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T33" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U33" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="V33" s="49" t="s">
+      <c r="V33" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="W33" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X33" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y33" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z33" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA33" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB33" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC33" s="49" t="s">
-        <v>1110</v>
+      <c r="W33" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X33" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y33" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z33" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA33" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB33" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC33" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="34" spans="1:29" ht="14.35" customHeight="1">
@@ -14409,13 +14397,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="45" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C34" s="46" t="s">
         <v>951</v>
       </c>
       <c r="D34" s="46" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="E34" s="48">
         <v>1</v>
@@ -14456,41 +14444,41 @@
       <c r="Q34" s="47">
         <v>0</v>
       </c>
-      <c r="R34" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S34" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T34" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U34" s="49" t="s">
+      <c r="R34" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S34" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T34" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U34" s="50" t="s">
         <v>952</v>
       </c>
-      <c r="V34" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W34" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X34" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y34" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z34" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA34" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB34" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC34" s="49" t="s">
-        <v>1110</v>
+      <c r="V34" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W34" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X34" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y34" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z34" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA34" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB34" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC34" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="35" spans="1:29" ht="14.35" customHeight="1">
@@ -14498,13 +14486,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="45" t="s">
-        <v>1013</v>
+        <v>1103</v>
       </c>
       <c r="C35" s="46" t="s">
-        <v>950</v>
+        <v>978</v>
       </c>
       <c r="D35" s="46" t="s">
-        <v>1077</v>
+        <v>1091</v>
       </c>
       <c r="E35" s="48">
         <v>1</v>
@@ -14545,41 +14533,41 @@
       <c r="Q35" s="47">
         <v>0</v>
       </c>
-      <c r="R35" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S35" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T35" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U35" s="49" t="s">
-        <v>29</v>
-      </c>
-      <c r="V35" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W35" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X35" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y35" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z35" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA35" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB35" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC35" s="49" t="s">
-        <v>1110</v>
+      <c r="R35" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S35" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T35" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U35" s="50" t="s">
+        <v>979</v>
+      </c>
+      <c r="V35" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W35" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X35" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y35" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z35" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA35" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB35" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC35" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="14.35" customHeight="1">
@@ -14587,13 +14575,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="45" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="C36" s="46" t="s">
-        <v>978</v>
+        <v>957</v>
       </c>
       <c r="D36" s="46" t="s">
-        <v>1092</v>
+        <v>1080</v>
       </c>
       <c r="E36" s="48">
         <v>1</v>
@@ -14634,41 +14622,41 @@
       <c r="Q36" s="47">
         <v>0</v>
       </c>
-      <c r="R36" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S36" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T36" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U36" s="49" t="s">
-        <v>979</v>
-      </c>
-      <c r="V36" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W36" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X36" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y36" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z36" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA36" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB36" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC36" s="49" t="s">
-        <v>1110</v>
+      <c r="R36" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S36" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T36" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U36" s="50" t="s">
+        <v>958</v>
+      </c>
+      <c r="V36" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W36" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X36" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y36" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z36" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA36" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB36" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC36" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="37" spans="1:29" ht="14.35" customHeight="1">
@@ -14676,13 +14664,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="45" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="C37" s="46" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="D37" s="46" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="E37" s="48">
         <v>1</v>
@@ -14723,41 +14711,41 @@
       <c r="Q37" s="47">
         <v>0</v>
       </c>
-      <c r="R37" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S37" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T37" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U37" s="49" t="s">
-        <v>958</v>
-      </c>
-      <c r="V37" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W37" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X37" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y37" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z37" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA37" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB37" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC37" s="49" t="s">
-        <v>1110</v>
+      <c r="R37" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S37" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T37" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U37" s="50" t="s">
+        <v>964</v>
+      </c>
+      <c r="V37" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W37" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X37" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y37" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z37" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA37" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB37" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC37" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="38" spans="1:29" ht="14.35" customHeight="1">
@@ -14765,31 +14753,31 @@
         <v>37</v>
       </c>
       <c r="B38" s="45" t="s">
-        <v>1105</v>
-      </c>
-      <c r="C38" s="46" t="s">
-        <v>963</v>
-      </c>
-      <c r="D38" s="46" t="s">
-        <v>1084</v>
+        <v>1109</v>
+      </c>
+      <c r="C38" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="45" t="s">
+        <v>1111</v>
       </c>
       <c r="E38" s="48">
+        <v>3</v>
+      </c>
+      <c r="F38" s="47">
         <v>1</v>
       </c>
-      <c r="F38" s="47">
-        <v>0</v>
-      </c>
       <c r="G38" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" s="47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" s="47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" s="47">
         <v>0</v>
@@ -14812,41 +14800,41 @@
       <c r="Q38" s="47">
         <v>0</v>
       </c>
-      <c r="R38" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S38" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T38" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U38" s="49" t="s">
-        <v>964</v>
-      </c>
-      <c r="V38" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W38" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X38" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y38" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z38" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA38" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB38" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC38" s="49" t="s">
-        <v>1110</v>
+      <c r="R38" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="S38" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="T38" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U38" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="V38" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W38" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X38" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y38" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z38" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA38" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB38" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC38" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="39" spans="1:29" ht="14.35" customHeight="1">
@@ -14854,16 +14842,16 @@
         <v>38</v>
       </c>
       <c r="B39" s="45" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C39" s="45" t="s">
+        <v>40</v>
+      </c>
+      <c r="D39" s="45" t="s">
         <v>1111</v>
       </c>
-      <c r="C39" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="D39" s="45" t="s">
-        <v>1113</v>
-      </c>
       <c r="E39" s="48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F39" s="47">
         <v>1</v>
@@ -14890,7 +14878,7 @@
         <v>0</v>
       </c>
       <c r="N39" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O39" s="47">
         <v>0</v>
@@ -14901,41 +14889,41 @@
       <c r="Q39" s="47">
         <v>0</v>
       </c>
-      <c r="R39" s="49" t="s">
-        <v>38</v>
-      </c>
-      <c r="S39" s="49" t="s">
-        <v>39</v>
-      </c>
-      <c r="T39" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U39" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="V39" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W39" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X39" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y39" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z39" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA39" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB39" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC39" s="49" t="s">
-        <v>1110</v>
+      <c r="R39" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="S39" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="T39" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U39" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="V39" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W39" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X39" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y39" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z39" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA39" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB39" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC39" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="40" spans="1:29" ht="14.35" customHeight="1">
@@ -14943,13 +14931,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="45" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C40" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" s="45" t="s">
         <v>1111</v>
-      </c>
-      <c r="C40" s="45" t="s">
-        <v>40</v>
-      </c>
-      <c r="D40" s="45" t="s">
-        <v>1113</v>
       </c>
       <c r="E40" s="48">
         <v>4</v>
@@ -14990,41 +14978,41 @@
       <c r="Q40" s="47">
         <v>0</v>
       </c>
-      <c r="R40" s="49" t="s">
-        <v>41</v>
-      </c>
-      <c r="S40" s="49" t="s">
-        <v>42</v>
-      </c>
-      <c r="T40" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U40" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="V40" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W40" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X40" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y40" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z40" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA40" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB40" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC40" s="49" t="s">
-        <v>1110</v>
+      <c r="R40" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="S40" s="50" t="s">
+        <v>45</v>
+      </c>
+      <c r="T40" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U40" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="V40" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W40" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X40" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y40" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z40" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA40" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB40" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC40" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="41" spans="1:29" ht="14.35" customHeight="1">
@@ -15032,13 +15020,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="45" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C41" s="45" t="s">
+        <v>46</v>
+      </c>
+      <c r="D41" s="45" t="s">
         <v>1111</v>
-      </c>
-      <c r="C41" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="D41" s="45" t="s">
-        <v>1113</v>
       </c>
       <c r="E41" s="48">
         <v>4</v>
@@ -15079,41 +15067,41 @@
       <c r="Q41" s="47">
         <v>0</v>
       </c>
-      <c r="R41" s="49" t="s">
-        <v>44</v>
-      </c>
-      <c r="S41" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="T41" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U41" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="V41" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W41" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X41" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y41" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z41" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA41" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB41" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC41" s="49" t="s">
-        <v>1110</v>
+      <c r="R41" s="50" t="s">
+        <v>47</v>
+      </c>
+      <c r="S41" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="T41" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U41" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="V41" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W41" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X41" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y41" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z41" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA41" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB41" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC41" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="42" spans="1:29" ht="14.35" customHeight="1">
@@ -15121,13 +15109,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="45" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C42" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="D42" s="45" t="s">
         <v>1111</v>
-      </c>
-      <c r="C42" s="45" t="s">
-        <v>46</v>
-      </c>
-      <c r="D42" s="45" t="s">
-        <v>1113</v>
       </c>
       <c r="E42" s="48">
         <v>4</v>
@@ -15168,41 +15156,41 @@
       <c r="Q42" s="47">
         <v>0</v>
       </c>
-      <c r="R42" s="49" t="s">
+      <c r="R42" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="S42" s="49" t="s">
-        <v>48</v>
-      </c>
-      <c r="T42" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U42" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="V42" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W42" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X42" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y42" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z42" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA42" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB42" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC42" s="49" t="s">
-        <v>1110</v>
+      <c r="S42" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="T42" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U42" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="V42" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W42" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X42" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y42" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z42" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA42" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB42" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC42" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="43" spans="1:29" ht="14.35" customHeight="1">
@@ -15210,13 +15198,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="45" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C43" s="45" t="s">
+        <v>51</v>
+      </c>
+      <c r="D43" s="45" t="s">
         <v>1111</v>
-      </c>
-      <c r="C43" s="45" t="s">
-        <v>49</v>
-      </c>
-      <c r="D43" s="45" t="s">
-        <v>1113</v>
       </c>
       <c r="E43" s="48">
         <v>4</v>
@@ -15257,41 +15245,41 @@
       <c r="Q43" s="47">
         <v>0</v>
       </c>
-      <c r="R43" s="49" t="s">
-        <v>47</v>
-      </c>
-      <c r="S43" s="49" t="s">
-        <v>50</v>
-      </c>
-      <c r="T43" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U43" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="V43" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W43" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X43" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y43" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z43" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA43" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB43" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC43" s="49" t="s">
-        <v>1110</v>
+      <c r="R43" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="S43" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="T43" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U43" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="V43" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W43" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X43" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y43" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z43" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA43" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB43" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC43" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="44" spans="1:29" ht="14.35" customHeight="1">
@@ -15299,32 +15287,32 @@
         <v>43</v>
       </c>
       <c r="B44" s="45" t="s">
-        <v>1111</v>
-      </c>
-      <c r="C44" s="45" t="s">
-        <v>51</v>
-      </c>
-      <c r="D44" s="45" t="s">
-        <v>1113</v>
+        <v>1109</v>
+      </c>
+      <c r="C44" s="46" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D44" s="46" t="s">
+        <v>1115</v>
       </c>
       <c r="E44" s="48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F44" s="47">
+        <v>0</v>
+      </c>
+      <c r="G44" s="47">
+        <v>0</v>
+      </c>
+      <c r="H44" s="47">
+        <v>0</v>
+      </c>
+      <c r="I44" s="47">
         <v>1</v>
       </c>
-      <c r="G44" s="47">
+      <c r="J44" s="47">
         <v>1</v>
       </c>
-      <c r="H44" s="47">
-        <v>1</v>
-      </c>
-      <c r="I44" s="47">
-        <v>0</v>
-      </c>
-      <c r="J44" s="47">
-        <v>0</v>
-      </c>
       <c r="K44" s="47">
         <v>0</v>
       </c>
@@ -15335,7 +15323,7 @@
         <v>0</v>
       </c>
       <c r="N44" s="47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" s="47">
         <v>0</v>
@@ -15346,41 +15334,41 @@
       <c r="Q44" s="47">
         <v>0</v>
       </c>
-      <c r="R44" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="S44" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="T44" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U44" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="V44" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W44" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X44" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y44" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z44" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA44" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB44" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC44" s="49" t="s">
-        <v>1110</v>
+      <c r="R44" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S44" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T44" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U44" s="50" t="s">
+        <v>994</v>
+      </c>
+      <c r="V44" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W44" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X44" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y44" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z44" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA44" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB44" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC44" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="45" spans="1:29" ht="14.35" customHeight="1">
@@ -15388,13 +15376,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="45" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="C45" s="46" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D45" s="46" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="E45" s="48">
         <v>1</v>
@@ -15435,41 +15423,41 @@
       <c r="Q45" s="47">
         <v>0</v>
       </c>
-      <c r="R45" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S45" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T45" s="49" t="s">
-        <v>1110</v>
+      <c r="R45" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S45" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T45" s="50" t="s">
+        <v>1108</v>
       </c>
       <c r="U45" s="49" t="s">
-        <v>995</v>
-      </c>
-      <c r="V45" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W45" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X45" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y45" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z45" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA45" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB45" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC45" s="49" t="s">
-        <v>1110</v>
+        <v>996</v>
+      </c>
+      <c r="V45" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W45" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X45" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y45" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z45" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA45" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB45" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC45" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="46" spans="1:29" ht="14.35" customHeight="1">
@@ -15477,13 +15465,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="45" t="s">
-        <v>1111</v>
+        <v>36</v>
       </c>
       <c r="C46" s="46" t="s">
-        <v>996</v>
+        <v>930</v>
       </c>
       <c r="D46" s="46" t="s">
-        <v>1101</v>
+        <v>1066</v>
       </c>
       <c r="E46" s="48">
         <v>1</v>
@@ -15524,41 +15512,41 @@
       <c r="Q46" s="47">
         <v>0</v>
       </c>
-      <c r="R46" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S46" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T46" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U46" s="49" t="s">
-        <v>997</v>
-      </c>
-      <c r="V46" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W46" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X46" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y46" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z46" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA46" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB46" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC46" s="49" t="s">
-        <v>1110</v>
+      <c r="R46" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S46" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T46" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U46" s="50" t="s">
+        <v>931</v>
+      </c>
+      <c r="V46" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W46" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X46" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y46" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z46" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA46" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB46" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC46" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="47" spans="1:29" ht="14.35" customHeight="1">
@@ -15569,10 +15557,10 @@
         <v>36</v>
       </c>
       <c r="C47" s="46" t="s">
-        <v>930</v>
-      </c>
-      <c r="D47" s="46" t="s">
-        <v>1067</v>
+        <v>967</v>
+      </c>
+      <c r="D47" s="45" t="s">
+        <v>1085</v>
       </c>
       <c r="E47" s="48">
         <v>1</v>
@@ -15613,135 +15601,46 @@
       <c r="Q47" s="47">
         <v>0</v>
       </c>
-      <c r="R47" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S47" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T47" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U47" s="49" t="s">
-        <v>931</v>
-      </c>
-      <c r="V47" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W47" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X47" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y47" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z47" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA47" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB47" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC47" s="49" t="s">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="48" spans="1:29" ht="14.35" customHeight="1">
-      <c r="A48" s="45">
-        <v>47</v>
-      </c>
-      <c r="B48" s="45" t="s">
-        <v>36</v>
-      </c>
-      <c r="C48" s="46" t="s">
-        <v>967</v>
-      </c>
-      <c r="D48" s="45" t="s">
-        <v>1086</v>
-      </c>
-      <c r="E48" s="48">
-        <v>1</v>
-      </c>
-      <c r="F48" s="47">
-        <v>0</v>
-      </c>
-      <c r="G48" s="47">
-        <v>0</v>
-      </c>
-      <c r="H48" s="47">
-        <v>0</v>
-      </c>
-      <c r="I48" s="47">
-        <v>1</v>
-      </c>
-      <c r="J48" s="47">
-        <v>1</v>
-      </c>
-      <c r="K48" s="47">
-        <v>0</v>
-      </c>
-      <c r="L48" s="47">
-        <v>0</v>
-      </c>
-      <c r="M48" s="47">
-        <v>0</v>
-      </c>
-      <c r="N48" s="47">
-        <v>0</v>
-      </c>
-      <c r="O48" s="47">
-        <v>0</v>
-      </c>
-      <c r="P48" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="47">
-        <v>0</v>
-      </c>
-      <c r="R48" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="S48" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="T48" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="U48" s="49" t="s">
+      <c r="R47" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="S47" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T47" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U47" s="50" t="s">
         <v>968</v>
       </c>
-      <c r="V48" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="W48" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="X48" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Y48" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="Z48" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AA48" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AB48" s="49" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AC48" s="49" t="s">
-        <v>1110</v>
+      <c r="V47" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W47" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X47" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Y47" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z47" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA47" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB47" s="50" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AC47" s="50" t="s">
+        <v>1108</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC48" xr:uid="{B93DC578-2EEA-48CF-9EFD-E294C2F4F9E2}"/>
-  <conditionalFormatting sqref="F2:Q48">
+  <autoFilter ref="A1:AC47" xr:uid="{B93DC578-2EEA-48CF-9EFD-E294C2F4F9E2}"/>
+  <conditionalFormatting sqref="F2:Q47">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
@@ -15752,6 +15651,8 @@
   <hyperlinks>
     <hyperlink ref="Z18" r:id="rId1" xr:uid="{A036A5ED-9977-4ADC-ACAC-863839E3A73F}"/>
     <hyperlink ref="U17" r:id="rId2" xr:uid="{3D76440B-DB1D-4A96-A329-B2E05A61B28D}"/>
+    <hyperlink ref="U31" r:id="rId3" xr:uid="{FED77476-3F3B-4268-ADD6-760E3385FC38}"/>
+    <hyperlink ref="U45" r:id="rId4" xr:uid="{876472B8-425C-44AE-9B8F-7C9E6ED5E9E1}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
